--- a/data/trans_bre/IP16B02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-69,28; -9,14</t>
+          <t>-62,56; -5,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 20,38</t>
+          <t>-21,69; 19,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 11,93</t>
+          <t>-44,99; 14,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-75,42; -12,07</t>
+          <t>-67,48; -7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 26,27</t>
+          <t>-22,75; 26,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,91; 14,79</t>
+          <t>-47,86; 17,43</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 13,8</t>
+          <t>-23,99; 14,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,3; -0,55</t>
+          <t>-34,79; -1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 16,29</t>
+          <t>-17,55; 16,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 15,98</t>
+          <t>-25,32; 16,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,44; -1,21</t>
+          <t>-36,65; -2,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 20,03</t>
+          <t>-18,51; 20,78</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 29,94</t>
+          <t>-5,05; 31,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 21,2</t>
+          <t>-19,37; 21,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 9,44</t>
+          <t>-32,29; 10,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 43,9</t>
+          <t>-4,9; 49,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 29,81</t>
+          <t>-21,48; 30,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 11,3</t>
+          <t>-35,24; 10,79</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 13,61</t>
+          <t>-30,09; 13,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 15,13</t>
+          <t>-22,7; 14,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 11,8</t>
+          <t>-21,21; 11,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 15,73</t>
+          <t>-33,5; 15,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 19,1</t>
+          <t>-24,51; 18,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 13,31</t>
+          <t>-22,42; 13,83</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 3,06</t>
+          <t>-21,95; 2,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 2,94</t>
+          <t>-16,6; 3,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 1,57</t>
+          <t>-17,29; 2,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 3,62</t>
+          <t>-24,49; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,24</t>
+          <t>-18,43; 3,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 1,78</t>
+          <t>-18,78; 3,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -5,49</t>
+          <t>-67,96; -8,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 19,92</t>
+          <t>-20,41; 20,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 14,09</t>
+          <t>-43,97; 13,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-67,48; -7,55</t>
+          <t>-73,98; -12,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 26,32</t>
+          <t>-21,12; 25,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 17,43</t>
+          <t>-46,77; 17,57</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 14,02</t>
+          <t>-27,49; 13,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -1,41</t>
+          <t>-34,4; 0,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 16,21</t>
+          <t>-18,21; 14,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 16,33</t>
+          <t>-28,86; 16,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,65; -2,5</t>
+          <t>-36,76; -1,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 20,78</t>
+          <t>-19,05; 18,62</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 31,41</t>
+          <t>-4,5; 30,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 21,21</t>
+          <t>-18,92; 18,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 10,27</t>
+          <t>-31,26; 8,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 49,58</t>
+          <t>-4,15; 47,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 30,1</t>
+          <t>-21,44; 25,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 10,79</t>
+          <t>-34,01; 9,88</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 13,28</t>
+          <t>-31,98; 13,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 14,93</t>
+          <t>-24,15; 15,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 11,74</t>
+          <t>-21,51; 11,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 15,39</t>
+          <t>-33,56; 15,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 18,93</t>
+          <t>-25,78; 20,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 13,83</t>
+          <t>-22,56; 13,78</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 2,46</t>
+          <t>-21,51; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 3,08</t>
+          <t>-16,78; 2,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 2,8</t>
+          <t>-17,94; 2,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 2,94</t>
+          <t>-23,73; 2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 3,31</t>
+          <t>-18,46; 2,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 3,19</t>
+          <t>-19,2; 2,48</t>
         </is>
       </c>
     </row>
